--- a/data/trans_orig/P35A_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P35A_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que siga una alimentación saludable en 2023</t>
+          <t>Población según si su médico le ha aconsejado que siga una alimentación saludable en 2023 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2783</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>887</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3054</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3147</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>887</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2740</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6221</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43507</t>
+          <t>43335</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70725</t>
+          <t>69273</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39072</t>
+          <t>40169</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57907</t>
+          <t>59586</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>89675</t>
+          <t>88792</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>123011</t>
+          <t>121527</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>238925</t>
+          <t>240663</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>266641</t>
+          <t>266759</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>230641</t>
+          <t>229150</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>249602</t>
+          <t>248212</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>475251</t>
+          <t>477174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>509545</t>
+          <t>510427</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,92%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58100</t>
+          <t>58750</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>103452</t>
+          <t>102144</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56505</t>
+          <t>56677</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>85577</t>
+          <t>84441</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>123191</t>
+          <t>123573</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>177469</t>
+          <t>176508</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>860</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13752</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>19306</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>122644</t>
+          <t>121177</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>175843</t>
+          <t>172917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111363</t>
+          <t>111225</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142928</t>
+          <t>143183</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>242683</t>
+          <t>243699</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>307211</t>
+          <t>307285</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>260253</t>
+          <t>258574</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>319053</t>
+          <t>322922</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>290856</t>
+          <t>290219</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>329993</t>
+          <t>328272</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>564530</t>
+          <t>563762</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>636551</t>
+          <t>633285</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,32%</t>
         </is>
       </c>
     </row>
@@ -1868,97 +1868,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1681</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>637</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4360</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3742</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3009</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -1981,97 +1981,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1319</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1681</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4110</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>1319</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>4647</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>4082</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>5339</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71741</t>
+          <t>69665</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98896</t>
+          <t>98338</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>66978</t>
+          <t>66224</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91468</t>
+          <t>90708</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>143930</t>
+          <t>144217</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>183051</t>
+          <t>183489</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>217154</t>
+          <t>217712</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>244309</t>
+          <t>246385</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>255270</t>
+          <t>255586</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>280521</t>
+          <t>280539</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>480176</t>
+          <t>479902</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>518347</t>
+          <t>518166</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>733</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>18755</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19696</t>
+          <t>18966</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9355</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>561</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11224</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53277</t>
+          <t>52860</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>86816</t>
+          <t>86065</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54971</t>
+          <t>56120</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>118330</t>
+          <t>120946</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>118561</t>
+          <t>109423</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>193942</t>
+          <t>191604</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>221508</t>
+          <t>220792</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>255880</t>
+          <t>255830</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>348382</t>
+          <t>345107</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>416228</t>
+          <t>414486</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>580712</t>
+          <t>584771</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>662177</t>
+          <t>672433</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>85,3%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12360</t>
+          <t>11384</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28352</t>
+          <t>27407</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11619</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25590</t>
+          <t>26460</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>26625</t>
+          <t>26990</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>48082</t>
+          <t>47731</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19663</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14473</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27913</t>
+          <t>27466</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20542</t>
+          <t>20343</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35505</t>
+          <t>35261</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28877</t>
+          <t>28853</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>43558</t>
+          <t>41755</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>52475</t>
+          <t>52905</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>72596</t>
+          <t>72120</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>109276</t>
+          <t>109659</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>129701</t>
+          <t>131143</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>137610</t>
+          <t>138331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>156817</t>
+          <t>156540</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>254755</t>
+          <t>254262</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282487</t>
+          <t>281895</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,84%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>11919</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>993</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>12942</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -3688,97 +3688,97 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1391</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>1216</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>61402</t>
+          <t>61481</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>86916</t>
+          <t>86145</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>55972</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>75428</t>
+          <t>76366</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>122983</t>
+          <t>122779</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>154742</t>
+          <t>153757</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>177850</t>
+          <t>178978</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>204097</t>
+          <t>203866</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>181628</t>
+          <t>180325</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>201495</t>
+          <t>200780</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>366656</t>
+          <t>366828</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>398341</t>
+          <t>399370</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,83%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18396</t>
+          <t>19060</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14316</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>23887</t>
+          <t>24612</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21956</t>
+          <t>20946</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>13845</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28954</t>
+          <t>28623</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>97940</t>
+          <t>96510</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>138554</t>
+          <t>136945</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>75127</t>
+          <t>69246</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>207123</t>
+          <t>206391</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>166008</t>
+          <t>170309</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>319623</t>
+          <t>324400</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>465061</t>
+          <t>467498</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>509571</t>
+          <t>511601</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>629327</t>
+          <t>630301</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>768944</t>
+          <t>775036</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1119811</t>
+          <t>1113779</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1288722</t>
+          <t>1283895</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>64722</t>
+          <t>65362</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>207604</t>
+          <t>207116</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>115379</t>
+          <t>114673</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>150032</t>
+          <t>149905</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>163628</t>
+          <t>163898</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>333194</t>
+          <t>335866</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>24597</t>
+          <t>27098</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>86644</t>
+          <t>86624</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>62458</t>
+          <t>61581</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>87291</t>
+          <t>87531</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>82929</t>
+          <t>83451</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>164208</t>
+          <t>165837</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>270934</t>
+          <t>269963</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>711687</t>
+          <t>710087</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>245594</t>
+          <t>246628</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>290283</t>
+          <t>293593</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>551401</t>
+          <t>546086</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1084985</t>
+          <t>1069489</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>64,96%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>124304</t>
+          <t>119010</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>380012</t>
+          <t>381044</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>221769</t>
+          <t>220346</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>265895</t>
+          <t>266793</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>314811</t>
+          <t>327029</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>617572</t>
+          <t>617535</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>203570</t>
+          <t>201115</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>299651</t>
+          <t>299922</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>187843</t>
+          <t>188587</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>261118</t>
+          <t>263072</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>429352</t>
+          <t>423486</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>542449</t>
+          <t>545458</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>65449</t>
+          <t>64626</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>107807</t>
+          <t>108413</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>79958</t>
+          <t>77182</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>119839</t>
+          <t>118295</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>158291</t>
+          <t>155921</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>218508</t>
+          <t>215692</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>821124</t>
+          <t>818537</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1538492</t>
+          <t>1552499</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>679621</t>
+          <t>703501</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>939244</t>
+          <t>950087</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1657581</t>
+          <t>1654042</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2547449</t>
+          <t>2478535</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1659202</t>
+          <t>1639125</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2273100</t>
+          <t>2275089</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2366842</t>
+          <t>2358953</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2703283</t>
+          <t>2699288</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4068758</t>
+          <t>4031073</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4795479</t>
+          <t>4786999</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P35A_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P35A_2023-Provincia-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>968</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>968</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>940</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>405</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55713</t>
+          <t>56996</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43335</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69273</t>
+          <t>69928</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49035</t>
+          <t>52963</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40169</t>
+          <t>43563</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59586</t>
+          <t>62702</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>104748</t>
+          <t>109959</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88792</t>
+          <t>94495</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>121527</t>
+          <t>125663</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>254705</t>
+          <t>260909</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>240663</t>
+          <t>247815</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>266759</t>
+          <t>273114</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>239308</t>
+          <t>261726</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>229150</t>
+          <t>251251</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>248212</t>
+          <t>271215</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>494012</t>
+          <t>522635</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>477174</t>
+          <t>506758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>510427</t>
+          <t>538018</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,74%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78062</t>
+          <t>80193</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58750</t>
+          <t>60846</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>102144</t>
+          <t>102825</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>69367</t>
+          <t>80112</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>56677</t>
+          <t>65659</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84441</t>
+          <t>97401</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>147429</t>
+          <t>160305</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>123573</t>
+          <t>134561</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>176508</t>
+          <t>186764</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -1407,102 +1407,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>9343</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>7923</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4320</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13859</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>11176</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>6503</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>19241</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>1,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8014</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4434</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13876</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>11204</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>6561</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>19306</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>146662</t>
+          <t>150706</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121177</t>
+          <t>126663</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>172917</t>
+          <t>178579</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>126777</t>
+          <t>132258</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111225</t>
+          <t>115529</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143183</t>
+          <t>149303</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>273439</t>
+          <t>282964</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>243699</t>
+          <t>251576</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>307285</t>
+          <t>313139</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>290477</t>
+          <t>296495</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>258574</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>322922</t>
+          <t>324400</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>310244</t>
+          <t>325605</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>290219</t>
+          <t>304861</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>328272</t>
+          <t>345932</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>600721</t>
+          <t>622100</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>563762</t>
+          <t>588616</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>633285</t>
+          <t>657405</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,07%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>514403</t>
+          <t>545898</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>514403</t>
+          <t>545898</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514403</t>
+          <t>545898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1032793</t>
+          <t>1076545</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1032793</t>
+          <t>1076545</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1032793</t>
+          <t>1076545</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>635</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>635</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>85024</t>
+          <t>85428</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69665</t>
+          <t>72147</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98338</t>
+          <t>100502</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>77492</t>
+          <t>79689</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>66224</t>
+          <t>68101</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90708</t>
+          <t>92736</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>162516</t>
+          <t>165117</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>144217</t>
+          <t>145132</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>183489</t>
+          <t>182961</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>231026</t>
+          <t>230565</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>217712</t>
+          <t>215491</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>246385</t>
+          <t>243846</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>269275</t>
+          <t>274329</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>255586</t>
+          <t>261619</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>280539</t>
+          <t>286298</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>500302</t>
+          <t>504894</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>479902</t>
+          <t>486650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>518166</t>
+          <t>524758</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,09%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>348723</t>
+          <t>355972</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>348723</t>
+          <t>355972</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>348723</t>
+          <t>355972</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>664774</t>
+          <t>671965</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>664774</t>
+          <t>671965</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>664774</t>
+          <t>671965</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>701</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18755</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>21974</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>955</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>12393</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>68442</t>
+          <t>86417</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52860</t>
+          <t>70109</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>86065</t>
+          <t>109981</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>92008</t>
+          <t>103941</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>87098</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>120946</t>
+          <t>121704</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>160449</t>
+          <t>190359</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>109423</t>
+          <t>164570</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>191604</t>
+          <t>217962</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -2771,102 +2771,102 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>239768</t>
+          <t>282074</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>220792</t>
+          <t>259343</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>255830</t>
+          <t>299067</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>69,5%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>80,15%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>310136</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>291641</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>327792</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>73,5%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>69,12%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>77,68%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>592210</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>561646</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>618450</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>74,48%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>70,64%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>81,85%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>376551</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>345107</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>414486</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>79,15%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>72,54%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>87,13%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>616317</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>584771</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>672433</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>78,19%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>74,18%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>77,78%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18758</t>
+          <t>21063</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>13513</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27407</t>
+          <t>31054</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17471</t>
+          <t>19585</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11485</t>
+          <t>13536</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26460</t>
+          <t>30795</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>36229</t>
+          <t>40648</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>26990</t>
+          <t>29500</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>47731</t>
+          <t>54625</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>12476</t>
+          <t>14056</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>21245</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>9532</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>15106</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>20417</t>
+          <t>23588</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>16804</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27466</t>
+          <t>32948</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>26710</t>
+          <t>29664</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20343</t>
+          <t>22438</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35261</t>
+          <t>39102</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>34952</t>
+          <t>36444</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28853</t>
+          <t>29821</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>41755</t>
+          <t>44361</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>61662</t>
+          <t>66108</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>52905</t>
+          <t>55493</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>72120</t>
+          <t>77071</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -3340,102 +3340,102 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>120797</t>
+          <t>140882</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>109659</t>
+          <t>128038</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>131143</t>
+          <t>150404</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
+          <t>73,13%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>161262</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>149852</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>170306</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>71,1%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>66,07%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>75,08%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>302144</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>284779</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>317324</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>69,86%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>65,85%</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
           <t>73,37%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>147911</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>138331</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>156540</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>71,02%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>66,42%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>75,16%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>268708</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>254262</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>281895</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>69,43%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>65,7%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>72,84%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>884</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>10268</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>660</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>72964</t>
+          <t>71252</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>61481</t>
+          <t>60424</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>86145</t>
+          <t>83209</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,17 +3831,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>65248</t>
+          <t>66951</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>55972</t>
+          <t>57431</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>76366</t>
+          <t>78724</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>138212</t>
+          <t>138203</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>122779</t>
+          <t>124023</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>153757</t>
+          <t>154458</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>192176</t>
+          <t>195484</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>178978</t>
+          <t>183266</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>203866</t>
+          <t>207424</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>191647</t>
+          <t>196139</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>180325</t>
+          <t>184407</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>200780</t>
+          <t>205949</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>383823</t>
+          <t>391623</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>366828</t>
+          <t>375454</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>399370</t>
+          <t>406937</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>76,14%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>12320</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>19060</t>
+          <t>24221</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>14842</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>12824</t>
+          <t>17615</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>24612</t>
+          <t>32613</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>9556</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20946</t>
+          <t>21766</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>14685</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>15955</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>9994</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28623</t>
+          <t>30693</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>116582</t>
+          <t>135615</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>96510</t>
+          <t>114343</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>136945</t>
+          <t>159719</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>150952</t>
+          <t>187867</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>69246</t>
+          <t>162276</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>206391</t>
+          <t>207984</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>267535</t>
+          <t>323482</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>170309</t>
+          <t>293208</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>324400</t>
+          <t>355495</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>489371</t>
+          <t>562196</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>467498</t>
+          <t>536590</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>511601</t>
+          <t>585158</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>687860</t>
+          <t>571683</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>630301</t>
+          <t>551162</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>775036</t>
+          <t>596470</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1177231</t>
+          <t>1133879</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1113779</t>
+          <t>1100227</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1283895</t>
+          <t>1166180</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>78,18%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>145972</t>
+          <t>177377</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>65362</t>
+          <t>152303</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>207116</t>
+          <t>202362</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>131997</t>
+          <t>154829</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>114673</t>
+          <t>133622</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>149905</t>
+          <t>177436</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>277970</t>
+          <t>332206</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>163898</t>
+          <t>299972</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>335866</t>
+          <t>365449</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>58728</t>
+          <t>68805</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>27098</t>
+          <t>54890</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>86624</t>
+          <t>85953</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>74065</t>
+          <t>85188</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>61581</t>
+          <t>71700</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>87531</t>
+          <t>101754</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>132793</t>
+          <t>153993</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>83451</t>
+          <t>133876</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>165837</t>
+          <t>177012</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>451140</t>
+          <t>230459</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>269963</t>
+          <t>204461</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>710087</t>
+          <t>256820</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>269275</t>
+          <t>301757</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>246628</t>
+          <t>276712</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>293593</t>
+          <t>327488</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>720416</t>
+          <t>532216</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>546086</t>
+          <t>497843</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1069489</t>
+          <t>570549</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>272880</t>
+          <t>321431</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>119010</t>
+          <t>292173</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>381044</t>
+          <t>349736</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>242394</t>
+          <t>289557</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>220346</t>
+          <t>264499</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>266793</t>
+          <t>317447</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>515274</t>
+          <t>610988</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>327029</t>
+          <t>574468</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>617535</t>
+          <t>650216</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>259003</t>
+          <t>297620</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>201115</t>
+          <t>260999</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>299922</t>
+          <t>336109</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>229188</t>
+          <t>267232</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>188587</t>
+          <t>238931</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>263072</t>
+          <t>301507</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>488192</t>
+          <t>564853</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>423486</t>
+          <t>519408</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>545458</t>
+          <t>613316</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>86377</t>
+          <t>98568</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>64626</t>
+          <t>78419</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>108413</t>
+          <t>120532</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>100687</t>
+          <t>114314</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>77182</t>
+          <t>97839</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>118295</t>
+          <t>134168</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>187064</t>
+          <t>212882</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>155921</t>
+          <t>186122</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>215692</t>
+          <t>239922</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1023237</t>
+          <t>846536</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>818537</t>
+          <t>796297</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1552499</t>
+          <t>906403</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>865740</t>
+          <t>961872</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>703501</t>
+          <t>917302</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>950087</t>
+          <t>1008674</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1888977</t>
+          <t>1808408</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1654042</t>
+          <t>1736253</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2478535</t>
+          <t>1882787</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2091200</t>
+          <t>2290037</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1639125</t>
+          <t>2224767</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2275089</t>
+          <t>2348590</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2465189</t>
+          <t>2390437</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2358953</t>
+          <t>2335252</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2699288</t>
+          <t>2437888</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>4556388</t>
+          <t>4680474</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4031073</t>
+          <t>4599983</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4786999</t>
+          <t>4760746</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>65,52%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3660804</t>
+          <t>3733855</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3660804</t>
+          <t>3733855</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3660804</t>
+          <t>3733855</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7120621</t>
+          <t>7266617</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7120621</t>
+          <t>7266617</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7120621</t>
+          <t>7266617</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
